--- a/docs/build/lakeshore-enterprise-context/source/12_ai_use_cases_moves/ai_opportunity_portfolio.xlsx
+++ b/docs/build/lakeshore-enterprise-context/source/12_ai_use_cases_moves/ai_opportunity_portfolio.xlsx
@@ -503,30 +503,30 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Reporting rationalization agent v0</t>
+          <t>Contract risk extractor v0</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Risk</t>
+          <t>Procurement</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>2.8</v>
+        <v>1.6</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>Low</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Strategic</t>
+          <t>Quick win</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Live</t>
+          <t>Scaling</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -543,16 +543,16 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Contract risk extractor v1</t>
+          <t>Incident summarizer v1</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Procurement</t>
+          <t>IT</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>5.6</v>
+        <v>6.5</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
@@ -561,17 +561,17 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Quick win</t>
+          <t>Foundational</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Live</t>
+          <t>Backlog</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Low</t>
+          <t>High</t>
         </is>
       </c>
     </row>
@@ -583,20 +583,20 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Close acceleration assistant v2</t>
+          <t>Cash forecasting copilot v2</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Data</t>
+          <t>Procurement</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>3.3</v>
+        <v>3.1</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Low</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -623,16 +623,16 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Contract risk extractor v3</t>
+          <t>SoD conflict detector v3</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Data</t>
+          <t>Procurement</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>3.8</v>
+        <v>5.5</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
@@ -646,7 +646,7 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Backlog</t>
+          <t>Scaling</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -663,30 +663,30 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Forecast variance explainer v0</t>
+          <t>Working capital optimizer v0</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Procurement</t>
+          <t>Data</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>4.4</v>
+        <v>2.9</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Foundational</t>
+          <t>Strategic</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Scaling</t>
+          <t>Pilot</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -703,16 +703,16 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Vendor scorecard agent v1</t>
+          <t>Incident summarizer v1</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Treasury</t>
+          <t>IT</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>8.5</v>
+        <v>6.4</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
@@ -721,7 +721,7 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Strategic</t>
+          <t>Foundational</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -731,7 +731,7 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>Low</t>
         </is>
       </c>
     </row>
@@ -743,7 +743,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>FX hedge advisor v2</t>
+          <t>Cash forecasting copilot v2</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -752,11 +752,11 @@
         </is>
       </c>
       <c r="D9" t="n">
-        <v>1.3</v>
+        <v>0.8</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Low</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -771,7 +771,7 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Low</t>
         </is>
       </c>
     </row>
@@ -783,7 +783,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Cash forecasting copilot v3</t>
+          <t>Liquidity scenario modeler v3</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -792,26 +792,26 @@
         </is>
       </c>
       <c r="D10" t="n">
-        <v>4.5</v>
+        <v>6.3</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Low</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Quick win</t>
+          <t>Strategic</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Scaling</t>
+          <t>Live</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>Low</t>
         </is>
       </c>
     </row>
@@ -823,7 +823,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Contract risk extractor v0</t>
+          <t>Spend optimization agent v0</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -832,7 +832,7 @@
         </is>
       </c>
       <c r="D11" t="n">
-        <v>3.4</v>
+        <v>8.6</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
@@ -846,12 +846,12 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Backlog</t>
+          <t>Scaling</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Low</t>
         </is>
       </c>
     </row>
@@ -863,35 +863,35 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Forecast variance explainer v1</t>
+          <t>Contract risk extractor v1</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Data</t>
+          <t>IT</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>5.3</v>
+        <v>2.2</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Low</t>
+          <t>High</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Strategic</t>
+          <t>Foundational</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Pilot</t>
+          <t>Scaling</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>Low</t>
+          <t>High</t>
         </is>
       </c>
     </row>
@@ -903,12 +903,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Knowledge deflection bot v2</t>
+          <t>SoD conflict detector v2</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>IT</t>
+          <t>Procurement</t>
         </is>
       </c>
       <c r="D13" t="n">
@@ -916,7 +916,7 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Low</t>
+          <t>High</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -926,12 +926,12 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Pilot</t>
+          <t>Scaling</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>Low</t>
+          <t>Medium</t>
         </is>
       </c>
     </row>
@@ -943,7 +943,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Audit evidence assembler v3</t>
+          <t>Contract risk extractor v3</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -952,11 +952,11 @@
         </is>
       </c>
       <c r="D14" t="n">
-        <v>1.7</v>
+        <v>2</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>Low</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -971,7 +971,7 @@
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>Low</t>
+          <t>Medium</t>
         </is>
       </c>
     </row>
@@ -983,16 +983,16 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Forecast variance explainer v0</t>
+          <t>Bank fee analyzer v0</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Risk</t>
+          <t>Treasury</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>6.8</v>
+        <v>7.5</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
@@ -1006,12 +1006,12 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Backlog</t>
+          <t>Scaling</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>Low</t>
+          <t>High</t>
         </is>
       </c>
     </row>
@@ -1023,35 +1023,35 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Contract risk extractor v1</t>
+          <t>Payment anomaly detection v1</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Data</t>
+          <t>Risk</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>1.1</v>
+        <v>2.9</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>High</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Strategic</t>
+          <t>Foundational</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Live</t>
+          <t>Scaling</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>Low</t>
         </is>
       </c>
     </row>
@@ -1063,25 +1063,25 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>FX hedge advisor v2</t>
+          <t>Payment anomaly detection v2</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Finance</t>
+          <t>Risk</t>
         </is>
       </c>
       <c r="D17" t="n">
-        <v>7.2</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Low</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Quick win</t>
+          <t>Strategic</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
@@ -1103,35 +1103,35 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Contract risk extractor v3</t>
+          <t>Bank fee analyzer v3</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Procurement</t>
+          <t>Treasury</t>
         </is>
       </c>
       <c r="D18" t="n">
-        <v>8.300000000000001</v>
+        <v>0.7</v>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Low</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Foundational</t>
+          <t>Quick win</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Pilot</t>
+          <t>Scaling</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>High</t>
         </is>
       </c>
     </row>
@@ -1143,16 +1143,16 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Vendor scorecard agent v0</t>
+          <t>Knowledge deflection bot v0</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Procurement</t>
+          <t>Finance</t>
         </is>
       </c>
       <c r="D19" t="n">
-        <v>8.300000000000001</v>
+        <v>8.9</v>
       </c>
       <c r="E19" t="inlineStr">
         <is>
@@ -1161,17 +1161,17 @@
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Strategic</t>
+          <t>Quick win</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Scaling</t>
+          <t>Live</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Medium</t>
         </is>
       </c>
     </row>
@@ -1183,20 +1183,20 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Spend optimization agent v1</t>
+          <t>SoD conflict detector v1</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Treasury</t>
+          <t>Data</t>
         </is>
       </c>
       <c r="D20" t="n">
-        <v>5.6</v>
+        <v>4</v>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>Low</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
@@ -1206,12 +1206,12 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Live</t>
+          <t>Backlog</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>Low</t>
         </is>
       </c>
     </row>
@@ -1223,20 +1223,20 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>FX hedge advisor v2</t>
+          <t>Cash forecasting copilot v2</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Finance</t>
+          <t>Procurement</t>
         </is>
       </c>
       <c r="D21" t="n">
-        <v>1.1</v>
+        <v>0.6</v>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
@@ -1246,12 +1246,12 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Backlog</t>
+          <t>Pilot</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Medium</t>
         </is>
       </c>
     </row>
@@ -1263,16 +1263,16 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Knowledge deflection bot v3</t>
+          <t>Contract risk extractor v3</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Risk</t>
+          <t>IT</t>
         </is>
       </c>
       <c r="D22" t="n">
-        <v>6.1</v>
+        <v>4.1</v>
       </c>
       <c r="E22" t="inlineStr">
         <is>
@@ -1281,7 +1281,7 @@
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Quick win</t>
+          <t>Foundational</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
@@ -1291,7 +1291,7 @@
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>Low</t>
         </is>
       </c>
     </row>
@@ -1303,35 +1303,35 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Forecast variance explainer v0</t>
+          <t>SoD conflict detector v0</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Treasury</t>
+          <t>IT</t>
         </is>
       </c>
       <c r="D23" t="n">
-        <v>8</v>
+        <v>0.4</v>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>Low</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Strategic</t>
+          <t>Foundational</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Scaling</t>
+          <t>Pilot</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>High</t>
         </is>
       </c>
     </row>
@@ -1343,16 +1343,16 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Bank fee analyzer v1</t>
+          <t>Close acceleration assistant v1</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Procurement</t>
+          <t>Risk</t>
         </is>
       </c>
       <c r="D24" t="n">
-        <v>8.300000000000001</v>
+        <v>2.6</v>
       </c>
       <c r="E24" t="inlineStr">
         <is>
@@ -1361,7 +1361,7 @@
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Foundational</t>
+          <t>Strategic</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
@@ -1383,35 +1383,35 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Forecast variance explainer v2</t>
+          <t>Liquidity scenario modeler v2</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Treasury</t>
+          <t>Data</t>
         </is>
       </c>
       <c r="D25" t="n">
-        <v>2.5</v>
+        <v>3.2</v>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>Low</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Foundational</t>
+          <t>Strategic</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Scaling</t>
+          <t>Pilot</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>Low</t>
         </is>
       </c>
     </row>
@@ -1423,35 +1423,35 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>FX hedge advisor v3</t>
+          <t>Close acceleration assistant v3</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Risk</t>
+          <t>Treasury</t>
         </is>
       </c>
       <c r="D26" t="n">
-        <v>6.6</v>
+        <v>5.7</v>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>Low</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Foundational</t>
+          <t>Quick win</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Live</t>
+          <t>Backlog</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Medium</t>
         </is>
       </c>
     </row>
@@ -1463,25 +1463,25 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Liquidity scenario modeler v0</t>
+          <t>Forecast variance explainer v0</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Risk</t>
+          <t>Data</t>
         </is>
       </c>
       <c r="D27" t="n">
-        <v>5.3</v>
+        <v>7.9</v>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>High</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Strategic</t>
+          <t>Foundational</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
@@ -1491,7 +1491,7 @@
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>Low</t>
+          <t>High</t>
         </is>
       </c>
     </row>
@@ -1503,25 +1503,25 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Audit evidence assembler v1</t>
+          <t>Spend optimization agent v1</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Data</t>
+          <t>Risk</t>
         </is>
       </c>
       <c r="D28" t="n">
-        <v>2.4</v>
+        <v>7.9</v>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Low</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Quick win</t>
+          <t>Foundational</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
@@ -1543,16 +1543,16 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Audit evidence assembler v2</t>
+          <t>Forecast variance explainer v2</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Procurement</t>
+          <t>Treasury</t>
         </is>
       </c>
       <c r="D29" t="n">
-        <v>2.8</v>
+        <v>2.2</v>
       </c>
       <c r="E29" t="inlineStr">
         <is>
@@ -1561,12 +1561,12 @@
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Quick win</t>
+          <t>Strategic</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Scaling</t>
+          <t>Pilot</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
@@ -1583,20 +1583,20 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Liquidity scenario modeler v3</t>
+          <t>Close acceleration assistant v3</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>IT</t>
+          <t>Data</t>
         </is>
       </c>
       <c r="D30" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Low</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
@@ -1606,12 +1606,12 @@
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Backlog</t>
+          <t>Live</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>Low</t>
+          <t>Medium</t>
         </is>
       </c>
     </row>
@@ -1628,11 +1628,11 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Finance</t>
+          <t>Procurement</t>
         </is>
       </c>
       <c r="D31" t="n">
-        <v>6.8</v>
+        <v>8.5</v>
       </c>
       <c r="E31" t="inlineStr">
         <is>
@@ -1641,17 +1641,17 @@
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Foundational</t>
+          <t>Strategic</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Backlog</t>
+          <t>Scaling</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>Low</t>
+          <t>High</t>
         </is>
       </c>
     </row>
@@ -1663,7 +1663,7 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Liquidity scenario modeler v1</t>
+          <t>Knowledge deflection bot v1</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -1672,26 +1672,26 @@
         </is>
       </c>
       <c r="D32" t="n">
-        <v>9</v>
+        <v>6.2</v>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Strategic</t>
+          <t>Quick win</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Pilot</t>
+          <t>Live</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>Low</t>
+          <t>High</t>
         </is>
       </c>
     </row>
@@ -1703,16 +1703,16 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>FX hedge advisor v2</t>
+          <t>Spend optimization agent v2</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Risk</t>
+          <t>Procurement</t>
         </is>
       </c>
       <c r="D33" t="n">
-        <v>7.5</v>
+        <v>4.6</v>
       </c>
       <c r="E33" t="inlineStr">
         <is>
@@ -1721,17 +1721,17 @@
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Strategic</t>
+          <t>Quick win</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Live</t>
+          <t>Pilot</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Low</t>
         </is>
       </c>
     </row>
@@ -1743,25 +1743,25 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Vendor scorecard agent v3</t>
+          <t>Incident summarizer v3</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Finance</t>
+          <t>Risk</t>
         </is>
       </c>
       <c r="D34" t="n">
-        <v>9.300000000000001</v>
+        <v>9.1</v>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>High</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Strategic</t>
+          <t>Quick win</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
@@ -1771,7 +1771,7 @@
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>Low</t>
+          <t>High</t>
         </is>
       </c>
     </row>
@@ -1783,12 +1783,12 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Contract risk extractor v0</t>
+          <t>Reporting rationalization agent v0</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Data</t>
+          <t>IT</t>
         </is>
       </c>
       <c r="D35" t="n">
@@ -1796,22 +1796,22 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Low</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Strategic</t>
+          <t>Foundational</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Backlog</t>
+          <t>Live</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Low</t>
         </is>
       </c>
     </row>
@@ -1823,16 +1823,16 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Reporting rationalization agent v1</t>
+          <t>Bank fee analyzer v1</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Procurement</t>
+          <t>IT</t>
         </is>
       </c>
       <c r="D36" t="n">
-        <v>3.6</v>
+        <v>8.1</v>
       </c>
       <c r="E36" t="inlineStr">
         <is>
@@ -1841,12 +1841,12 @@
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Foundational</t>
+          <t>Quick win</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Scaling</t>
+          <t>Backlog</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
@@ -1872,7 +1872,7 @@
         </is>
       </c>
       <c r="D37" t="n">
-        <v>4</v>
+        <v>0.7</v>
       </c>
       <c r="E37" t="inlineStr">
         <is>
@@ -1881,7 +1881,7 @@
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Strategic</t>
+          <t>Quick win</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
@@ -1903,30 +1903,30 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Vendor scorecard agent v3</t>
+          <t>Audit evidence assembler v3</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Treasury</t>
+          <t>IT</t>
         </is>
       </c>
       <c r="D38" t="n">
-        <v>2.3</v>
+        <v>7</v>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Low</t>
+          <t>High</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Foundational</t>
+          <t>Quick win</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Pilot</t>
+          <t>Live</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
@@ -1943,16 +1943,16 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Audit evidence assembler v0</t>
+          <t>Reporting rationalization agent v0</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Treasury</t>
+          <t>Procurement</t>
         </is>
       </c>
       <c r="D39" t="n">
-        <v>5.3</v>
+        <v>4.1</v>
       </c>
       <c r="E39" t="inlineStr">
         <is>
@@ -1961,17 +1961,17 @@
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Strategic</t>
+          <t>Quick win</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Scaling</t>
+          <t>Pilot</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Low</t>
         </is>
       </c>
     </row>
@@ -1983,7 +1983,7 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Contract risk extractor v1</t>
+          <t>Knowledge deflection bot v1</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -1992,16 +1992,16 @@
         </is>
       </c>
       <c r="D40" t="n">
-        <v>8</v>
+        <v>8.9</v>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>High</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Quick win</t>
+          <t>Strategic</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
@@ -2011,7 +2011,7 @@
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Medium</t>
         </is>
       </c>
     </row>
@@ -2023,7 +2023,7 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Liquidity scenario modeler v2</t>
+          <t>Spend optimization agent v2</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
@@ -2032,7 +2032,7 @@
         </is>
       </c>
       <c r="D41" t="n">
-        <v>2.6</v>
+        <v>6.9</v>
       </c>
       <c r="E41" t="inlineStr">
         <is>
@@ -2046,12 +2046,12 @@
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Pilot</t>
+          <t>Backlog</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>High</t>
         </is>
       </c>
     </row>
@@ -2063,16 +2063,16 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Payment anomaly detection v3</t>
+          <t>Close acceleration assistant v3</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>IT</t>
+          <t>Treasury</t>
         </is>
       </c>
       <c r="D42" t="n">
-        <v>3.6</v>
+        <v>7.3</v>
       </c>
       <c r="E42" t="inlineStr">
         <is>
@@ -2081,17 +2081,17 @@
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Quick win</t>
+          <t>Foundational</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Pilot</t>
+          <t>Backlog</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Medium</t>
         </is>
       </c>
     </row>
@@ -2103,20 +2103,20 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Liquidity scenario modeler v0</t>
+          <t>Forecast variance explainer v0</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Risk</t>
+          <t>Finance</t>
         </is>
       </c>
       <c r="D43" t="n">
-        <v>3.9</v>
+        <v>6.5</v>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>Low</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
@@ -2126,12 +2126,12 @@
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Pilot</t>
+          <t>Live</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>High</t>
         </is>
       </c>
     </row>
@@ -2143,35 +2143,35 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Spend optimization agent v1</t>
+          <t>Payment anomaly detection v1</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Treasury</t>
+          <t>Risk</t>
         </is>
       </c>
       <c r="D44" t="n">
-        <v>8</v>
+        <v>7.2</v>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>High</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Quick win</t>
+          <t>Foundational</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Scaling</t>
+          <t>Pilot</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>Low</t>
         </is>
       </c>
     </row>
@@ -2183,35 +2183,35 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Cash forecasting copilot v2</t>
+          <t>Contract risk extractor v2</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Risk</t>
+          <t>Data</t>
         </is>
       </c>
       <c r="D45" t="n">
-        <v>8.800000000000001</v>
+        <v>3.7</v>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>Low</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Quick win</t>
+          <t>Foundational</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Live</t>
+          <t>Scaling</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>Low</t>
+          <t>Medium</t>
         </is>
       </c>
     </row>
@@ -2223,25 +2223,25 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Reporting rationalization agent v3</t>
+          <t>Payment anomaly detection v3</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Treasury</t>
+          <t>Finance</t>
         </is>
       </c>
       <c r="D46" t="n">
-        <v>1.2</v>
+        <v>5</v>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>Low</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Quick win</t>
+          <t>Strategic</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
@@ -2251,7 +2251,7 @@
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>Low</t>
         </is>
       </c>
     </row>
@@ -2263,35 +2263,35 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Liquidity scenario modeler v0</t>
+          <t>Spend optimization agent v0</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Finance</t>
+          <t>Procurement</t>
         </is>
       </c>
       <c r="D47" t="n">
-        <v>4.7</v>
+        <v>1.5</v>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Low</t>
+          <t>High</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Quick win</t>
+          <t>Foundational</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Backlog</t>
+          <t>Pilot</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>Low</t>
         </is>
       </c>
     </row>
@@ -2303,20 +2303,20 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Working capital optimizer v1</t>
+          <t>Cash forecasting copilot v1</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>IT</t>
+          <t>Data</t>
         </is>
       </c>
       <c r="D48" t="n">
-        <v>8.699999999999999</v>
+        <v>3</v>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>High</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
@@ -2343,16 +2343,16 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Liquidity scenario modeler v2</t>
+          <t>Knowledge deflection bot v2</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Finance</t>
+          <t>Risk</t>
         </is>
       </c>
       <c r="D49" t="n">
-        <v>9.4</v>
+        <v>4.9</v>
       </c>
       <c r="E49" t="inlineStr">
         <is>
@@ -2361,17 +2361,17 @@
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Strategic</t>
+          <t>Foundational</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Backlog</t>
+          <t>Scaling</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>High</t>
         </is>
       </c>
     </row>
@@ -2383,7 +2383,7 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Vendor scorecard agent v3</t>
+          <t>Audit evidence assembler v3</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
@@ -2392,7 +2392,7 @@
         </is>
       </c>
       <c r="D50" t="n">
-        <v>8.1</v>
+        <v>6.8</v>
       </c>
       <c r="E50" t="inlineStr">
         <is>
@@ -2401,7 +2401,7 @@
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Foundational</t>
+          <t>Quick win</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
@@ -2411,7 +2411,7 @@
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>Low</t>
+          <t>Medium</t>
         </is>
       </c>
     </row>
@@ -2423,30 +2423,30 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Bank fee analyzer v0</t>
+          <t>Vendor scorecard agent v0</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>IT</t>
+          <t>Finance</t>
         </is>
       </c>
       <c r="D51" t="n">
-        <v>8.9</v>
+        <v>0.8</v>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Low</t>
+          <t>High</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Quick win</t>
+          <t>Strategic</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Pilot</t>
+          <t>Backlog</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
@@ -2468,20 +2468,20 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>IT</t>
+          <t>Finance</t>
         </is>
       </c>
       <c r="D52" t="n">
-        <v>6.8</v>
+        <v>5</v>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>Low</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Quick win</t>
+          <t>Foundational</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
@@ -2491,7 +2491,7 @@
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Low</t>
         </is>
       </c>
     </row>
@@ -2503,25 +2503,25 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>Contract risk extractor v2</t>
+          <t>FX hedge advisor v2</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Procurement</t>
+          <t>Treasury</t>
         </is>
       </c>
       <c r="D53" t="n">
-        <v>2.8</v>
+        <v>6.7</v>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>Low</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Foundational</t>
+          <t>Strategic</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
@@ -2531,7 +2531,7 @@
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>Low</t>
+          <t>High</t>
         </is>
       </c>
     </row>
@@ -2543,20 +2543,20 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>Knowledge deflection bot v3</t>
+          <t>Vendor scorecard agent v3</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Data</t>
+          <t>Treasury</t>
         </is>
       </c>
       <c r="D54" t="n">
-        <v>8.5</v>
+        <v>1.8</v>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>High</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
@@ -2566,7 +2566,7 @@
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Live</t>
+          <t>Backlog</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
@@ -2583,30 +2583,30 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>Close acceleration assistant v0</t>
+          <t>Forecast variance explainer v0</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Treasury</t>
+          <t>Procurement</t>
         </is>
       </c>
       <c r="D55" t="n">
-        <v>8.199999999999999</v>
+        <v>5.1</v>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Low</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Quick win</t>
+          <t>Foundational</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Live</t>
+          <t>Backlog</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
@@ -2623,7 +2623,7 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>Spend optimization agent v1</t>
+          <t>Payment anomaly detection v1</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
@@ -2632,7 +2632,7 @@
         </is>
       </c>
       <c r="D56" t="n">
-        <v>5.1</v>
+        <v>4.5</v>
       </c>
       <c r="E56" t="inlineStr">
         <is>
@@ -2646,12 +2646,12 @@
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Live</t>
+          <t>Backlog</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Low</t>
         </is>
       </c>
     </row>
@@ -2663,35 +2663,35 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>Working capital optimizer v2</t>
+          <t>Knowledge deflection bot v2</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Treasury</t>
+          <t>Risk</t>
         </is>
       </c>
       <c r="D57" t="n">
-        <v>6.9</v>
+        <v>3.7</v>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Low</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Foundational</t>
+          <t>Quick win</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Scaling</t>
+          <t>Backlog</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>High</t>
         </is>
       </c>
     </row>
@@ -2703,16 +2703,16 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>Vendor scorecard agent v3</t>
+          <t>Audit evidence assembler v3</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Treasury</t>
+          <t>Risk</t>
         </is>
       </c>
       <c r="D58" t="n">
-        <v>1.2</v>
+        <v>5.1</v>
       </c>
       <c r="E58" t="inlineStr">
         <is>
@@ -2721,17 +2721,17 @@
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Strategic</t>
+          <t>Quick win</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Backlog</t>
+          <t>Scaling</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>High</t>
         </is>
       </c>
     </row>
@@ -2743,35 +2743,35 @@
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>Audit evidence assembler v0</t>
+          <t>Close acceleration assistant v0</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Procurement</t>
+          <t>Data</t>
         </is>
       </c>
       <c r="D59" t="n">
-        <v>4.8</v>
+        <v>7.7</v>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>Low</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Strategic</t>
+          <t>Foundational</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Pilot</t>
+          <t>Scaling</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>Low</t>
+          <t>Medium</t>
         </is>
       </c>
     </row>
@@ -2783,20 +2783,20 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>Reporting rationalization agent v1</t>
+          <t>Working capital optimizer v1</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Risk</t>
+          <t>Finance</t>
         </is>
       </c>
       <c r="D60" t="n">
-        <v>8.4</v>
+        <v>4</v>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>Low</t>
+          <t>High</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
@@ -2806,7 +2806,7 @@
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Backlog</t>
+          <t>Scaling</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
@@ -2823,16 +2823,16 @@
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>Incident summarizer v2</t>
+          <t>Cash forecasting copilot v2</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Data</t>
+          <t>Risk</t>
         </is>
       </c>
       <c r="D61" t="n">
-        <v>3.6</v>
+        <v>7.6</v>
       </c>
       <c r="E61" t="inlineStr">
         <is>
@@ -2851,7 +2851,7 @@
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Medium</t>
         </is>
       </c>
     </row>
@@ -2863,30 +2863,30 @@
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>Forecast variance explainer v3</t>
+          <t>FX hedge advisor v3</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Treasury</t>
+          <t>IT</t>
         </is>
       </c>
       <c r="D62" t="n">
-        <v>8</v>
+        <v>4.3</v>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Low</t>
+          <t>High</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Strategic</t>
+          <t>Quick win</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Backlog</t>
+          <t>Pilot</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
